--- a/public/sap-reporting/expansion-150-downloads/EXT-QM10-01.xlsx
+++ b/public/sap-reporting/expansion-150-downloads/EXT-QM10-01.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="Rc9742441dd004a67"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="Rf278e33c728e478c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="Rab75bc76dc744c40"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="R6c318a5c263a4cd8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="R339c95b73c6f4f94"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="Ra385b957cb504e67"/>
   </x:sheets>
 </x:workbook>
 </file>
